--- a/data/trans_orig/P57_R2-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P57_R2-Habitat-trans_orig.xlsx
@@ -536,7 +536,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con autopercepción de la felicidad mayor o igual a 9 (Likert 0 a 10) en 2016</t>
+          <t>Población con autopercepción de la felicidad mayor o igual a 9 (Likert 0 a 10) en 2016 (tasa de respuesta: 99,57%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -731,12 +731,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>177957</t>
+          <t>178245</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>225874</t>
+          <t>226061</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -746,12 +746,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>26,58%</t>
+          <t>26,62%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>33,74%</t>
+          <t>33,77%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -766,12 +766,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>155019</t>
+          <t>155361</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>196699</t>
+          <t>199002</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -781,12 +781,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>23,23%</t>
+          <t>23,28%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>29,47%</t>
+          <t>29,82%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -801,12 +801,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>342326</t>
+          <t>344680</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>409813</t>
+          <t>412268</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -816,12 +816,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>25,61%</t>
+          <t>25,78%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>30,65%</t>
+          <t>30,84%</t>
         </is>
       </c>
     </row>
@@ -844,12 +844,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>443619</t>
+          <t>443432</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>491536</t>
+          <t>491248</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -859,12 +859,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>66,26%</t>
+          <t>66,23%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>73,42%</t>
+          <t>73,38%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -879,12 +879,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>470695</t>
+          <t>468392</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>512375</t>
+          <t>512033</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -894,12 +894,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>70,53%</t>
+          <t>70,18%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>76,77%</t>
+          <t>76,72%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -914,12 +914,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>927074</t>
+          <t>924619</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>994561</t>
+          <t>992207</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -929,12 +929,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>69,35%</t>
+          <t>69,16%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>74,39%</t>
+          <t>74,22%</t>
         </is>
       </c>
     </row>
@@ -1074,12 +1074,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>269587</t>
+          <t>271139</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>331173</t>
+          <t>332905</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1089,12 +1089,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>26,4%</t>
+          <t>26,55%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>32,43%</t>
+          <t>32,6%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>247931</t>
+          <t>244648</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>305019</t>
+          <t>305485</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1124,12 +1124,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>23,8%</t>
+          <t>23,48%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>29,27%</t>
+          <t>29,32%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1144,12 +1144,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>539006</t>
+          <t>532097</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>617742</t>
+          <t>616288</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>26,12%</t>
+          <t>25,79%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>29,94%</t>
+          <t>29,87%</t>
         </is>
       </c>
     </row>
@@ -1187,12 +1187,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>690156</t>
+          <t>688424</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>751742</t>
+          <t>750190</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1202,12 +1202,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>67,57%</t>
+          <t>67,4%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>73,6%</t>
+          <t>73,45%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1222,12 +1222,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>736917</t>
+          <t>736451</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>794005</t>
+          <t>797288</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1237,12 +1237,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>70,73%</t>
+          <t>70,68%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>76,2%</t>
+          <t>76,52%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1257,12 +1257,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1445523</t>
+          <t>1446977</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1524259</t>
+          <t>1531168</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1272,12 +1272,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>70,06%</t>
+          <t>70,13%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>73,88%</t>
+          <t>74,21%</t>
         </is>
       </c>
     </row>
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>203123</t>
+          <t>203617</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>255594</t>
+          <t>253376</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1432,12 +1432,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>26,85%</t>
+          <t>26,92%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>33,79%</t>
+          <t>33,5%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1452,12 +1452,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>175400</t>
+          <t>175356</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>225812</t>
+          <t>222401</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1467,12 +1467,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>22,51%</t>
+          <t>22,5%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>28,98%</t>
+          <t>28,54%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1487,12 +1487,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>391293</t>
+          <t>391016</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>460647</t>
+          <t>462673</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1502,12 +1502,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>25,48%</t>
+          <t>25,46%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>30,0%</t>
+          <t>30,13%</t>
         </is>
       </c>
     </row>
@@ -1530,12 +1530,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>500845</t>
+          <t>503063</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>553316</t>
+          <t>552822</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1545,12 +1545,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>66,21%</t>
+          <t>66,5%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>73,15%</t>
+          <t>73,08%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1565,12 +1565,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>553493</t>
+          <t>556904</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>603905</t>
+          <t>603949</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1580,12 +1580,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>71,02%</t>
+          <t>71,46%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>77,49%</t>
+          <t>77,5%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1600,12 +1600,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1075097</t>
+          <t>1073071</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1144451</t>
+          <t>1144728</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1615,12 +1615,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>70,0%</t>
+          <t>69,87%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>74,52%</t>
+          <t>74,54%</t>
         </is>
       </c>
     </row>
@@ -1760,12 +1760,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>272701</t>
+          <t>271200</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>328930</t>
+          <t>323922</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1775,12 +1775,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>29,21%</t>
+          <t>29,05%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>35,24%</t>
+          <t>34,7%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1795,12 +1795,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>249378</t>
+          <t>249316</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>306980</t>
+          <t>309195</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1810,12 +1810,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>23,99%</t>
+          <t>23,98%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>29,53%</t>
+          <t>29,75%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1830,12 +1830,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>541688</t>
+          <t>535938</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>620107</t>
+          <t>620546</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1845,12 +1845,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>27,46%</t>
+          <t>27,16%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>31,43%</t>
+          <t>31,45%</t>
         </is>
       </c>
     </row>
@@ -1873,12 +1873,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>604543</t>
+          <t>609551</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>660772</t>
+          <t>662273</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1888,12 +1888,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>64,76%</t>
+          <t>65,3%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>70,79%</t>
+          <t>70,95%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1908,12 +1908,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>732487</t>
+          <t>730272</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>790089</t>
+          <t>790151</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1923,12 +1923,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>70,47%</t>
+          <t>70,25%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>76,01%</t>
+          <t>76,02%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1943,12 +1943,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1352833</t>
+          <t>1352394</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1431252</t>
+          <t>1437002</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1958,12 +1958,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>68,57%</t>
+          <t>68,55%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>72,54%</t>
+          <t>72,84%</t>
         </is>
       </c>
     </row>
@@ -2103,12 +2103,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>977133</t>
+          <t>977737</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>1087918</t>
+          <t>1087075</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2118,12 +2118,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>28,9%</t>
+          <t>28,92%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>32,18%</t>
+          <t>32,15%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2138,12 +2138,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>877663</t>
+          <t>877838</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>981482</t>
+          <t>976656</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2158,7 +2158,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>27,82%</t>
+          <t>27,68%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2173,12 +2173,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1875864</t>
+          <t>1880581</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>2028846</t>
+          <t>2033723</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2188,12 +2188,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>27,15%</t>
+          <t>27,22%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>29,37%</t>
+          <t>29,44%</t>
         </is>
       </c>
     </row>
@@ -2216,12 +2216,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2292815</t>
+          <t>2293658</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2403600</t>
+          <t>2402996</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2231,12 +2231,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>67,82%</t>
+          <t>67,85%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>71,1%</t>
+          <t>71,08%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2251,12 +2251,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2546622</t>
+          <t>2551448</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>2650441</t>
+          <t>2650266</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2266,7 +2266,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>72,18%</t>
+          <t>72,32%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2286,12 +2286,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>4879991</t>
+          <t>4875114</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>5032973</t>
+          <t>5028256</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2301,12 +2301,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>70,63%</t>
+          <t>70,56%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>72,85%</t>
+          <t>72,78%</t>
         </is>
       </c>
     </row>
@@ -2483,7 +2483,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con autopercepción de la felicidad mayor o igual a 9 (Likert 0 a 10) en 2023</t>
+          <t>Población con autopercepción de la felicidad mayor o igual a 9 (Likert 0 a 10) en 2023 (tasa de respuesta: 99,4%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2678,12 +2678,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>238992</t>
+          <t>239648</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>294960</t>
+          <t>295651</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2693,12 +2693,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>38,02%</t>
+          <t>38,12%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>46,92%</t>
+          <t>47,03%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2713,12 +2713,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>247811</t>
+          <t>249991</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>290156</t>
+          <t>290294</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2728,12 +2728,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>36,97%</t>
+          <t>37,3%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>43,29%</t>
+          <t>43,31%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2748,12 +2748,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>505291</t>
+          <t>505380</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>574280</t>
+          <t>572669</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2763,12 +2763,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>38,9%</t>
+          <t>38,91%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>44,21%</t>
+          <t>44,09%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>333659</t>
+          <t>332968</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>389627</t>
+          <t>388971</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>53,08%</t>
+          <t>52,97%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>61,98%</t>
+          <t>61,88%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>380080</t>
+          <t>379942</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>422425</t>
+          <t>420245</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>56,71%</t>
+          <t>56,69%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>63,03%</t>
+          <t>62,7%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>724575</t>
+          <t>726186</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>793564</t>
+          <t>793475</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>55,79%</t>
+          <t>55,91%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>61,1%</t>
+          <t>61,09%</t>
         </is>
       </c>
     </row>
@@ -3021,12 +3021,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>573025</t>
+          <t>576343</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>929244</t>
+          <t>947872</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3036,12 +3036,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>48,09%</t>
+          <t>48,37%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>77,99%</t>
+          <t>79,55%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3056,12 +3056,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>373970</t>
+          <t>373498</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>427332</t>
+          <t>428954</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3071,12 +3071,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>39,38%</t>
+          <t>39,33%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>44,99%</t>
+          <t>45,16%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3091,12 +3091,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>967933</t>
+          <t>968336</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1455433</t>
+          <t>1497473</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3106,12 +3106,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>45,2%</t>
+          <t>45,22%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>67,97%</t>
+          <t>69,93%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>262271</t>
+          <t>243643</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>618490</t>
+          <t>615172</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>22,01%</t>
+          <t>20,45%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>51,91%</t>
+          <t>51,63%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>522423</t>
+          <t>520801</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>575785</t>
+          <t>576257</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>55,01%</t>
+          <t>54,84%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>60,62%</t>
+          <t>60,67%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>685837</t>
+          <t>643797</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1173337</t>
+          <t>1172934</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>32,03%</t>
+          <t>30,07%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>54,8%</t>
+          <t>54,78%</t>
         </is>
       </c>
     </row>
@@ -3364,12 +3364,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>353839</t>
+          <t>356589</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>412136</t>
+          <t>414028</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3379,12 +3379,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>50,21%</t>
+          <t>50,6%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>58,49%</t>
+          <t>58,75%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3399,12 +3399,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>179655</t>
+          <t>178497</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>449351</t>
+          <t>449726</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3414,12 +3414,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>19,33%</t>
+          <t>19,2%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>48,34%</t>
+          <t>48,38%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3434,12 +3434,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>427563</t>
+          <t>453826</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>846887</t>
+          <t>844556</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3449,12 +3449,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>26,16%</t>
+          <t>27,77%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>51,82%</t>
+          <t>51,68%</t>
         </is>
       </c>
     </row>
@@ -3477,12 +3477,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>292544</t>
+          <t>290652</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>350841</t>
+          <t>348091</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3492,12 +3492,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>41,51%</t>
+          <t>41,25%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>49,79%</t>
+          <t>49,4%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3512,12 +3512,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>480144</t>
+          <t>479769</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>749840</t>
+          <t>750998</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3527,12 +3527,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>51,66%</t>
+          <t>51,62%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>80,67%</t>
+          <t>80,8%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3547,12 +3547,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>787289</t>
+          <t>789620</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1206613</t>
+          <t>1180350</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3562,12 +3562,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>48,18%</t>
+          <t>48,32%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>73,84%</t>
+          <t>72,23%</t>
         </is>
       </c>
     </row>
@@ -3707,12 +3707,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>349310</t>
+          <t>349174</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>415559</t>
+          <t>413701</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3722,12 +3722,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>37,77%</t>
+          <t>37,76%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>44,93%</t>
+          <t>44,73%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3742,12 +3742,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>302012</t>
+          <t>297458</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>410303</t>
+          <t>408269</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3757,12 +3757,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>27,69%</t>
+          <t>27,27%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>37,61%</t>
+          <t>37,43%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3777,12 +3777,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>666760</t>
+          <t>672675</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>804386</t>
+          <t>808724</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3792,12 +3792,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>33,08%</t>
+          <t>33,37%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>39,91%</t>
+          <t>40,12%</t>
         </is>
       </c>
     </row>
@@ -3820,12 +3820,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>509260</t>
+          <t>511118</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>575509</t>
+          <t>575645</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3835,12 +3835,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>55,07%</t>
+          <t>55,27%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>62,23%</t>
+          <t>62,24%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3855,12 +3855,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>680527</t>
+          <t>682561</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>788818</t>
+          <t>793372</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3870,12 +3870,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>62,39%</t>
+          <t>62,57%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>72,31%</t>
+          <t>72,73%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3890,12 +3890,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1211263</t>
+          <t>1206925</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1348889</t>
+          <t>1342974</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3905,12 +3905,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>60,09%</t>
+          <t>59,88%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>66,92%</t>
+          <t>66,63%</t>
         </is>
       </c>
     </row>
@@ -4050,12 +4050,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1597551</t>
+          <t>1598032</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>2146360</t>
+          <t>2134364</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4065,12 +4065,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>46,31%</t>
+          <t>46,32%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>62,22%</t>
+          <t>61,87%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4085,12 +4085,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1122807</t>
+          <t>1098223</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>1496713</t>
+          <t>1489538</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4100,12 +4100,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>30,84%</t>
+          <t>30,17%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>41,11%</t>
+          <t>40,92%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4120,12 +4120,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>2883072</t>
+          <t>2875021</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>3555898</t>
+          <t>3560702</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4135,12 +4135,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>40,66%</t>
+          <t>40,55%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>50,15%</t>
+          <t>50,22%</t>
         </is>
       </c>
     </row>
@@ -4163,12 +4163,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1303273</t>
+          <t>1315269</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1852082</t>
+          <t>1851601</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4178,12 +4178,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>37,78%</t>
+          <t>38,13%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>53,69%</t>
+          <t>53,68%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4198,12 +4198,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2143603</t>
+          <t>2150778</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>2517509</t>
+          <t>2542093</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4213,12 +4213,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>58,89%</t>
+          <t>59,08%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>69,16%</t>
+          <t>69,83%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4233,12 +4233,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>3534051</t>
+          <t>3529247</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>4206877</t>
+          <t>4214928</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4248,12 +4248,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>49,85%</t>
+          <t>49,78%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>59,34%</t>
+          <t>59,45%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P57_R2-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P57_R2-Habitat-trans_orig.xlsx
@@ -731,12 +731,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>178245</t>
+          <t>175492</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>226061</t>
+          <t>225573</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -746,12 +746,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>26,62%</t>
+          <t>26,21%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>33,77%</t>
+          <t>33,69%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -766,12 +766,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>155361</t>
+          <t>153435</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>199002</t>
+          <t>198237</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -781,12 +781,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>23,28%</t>
+          <t>22,99%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>29,82%</t>
+          <t>29,7%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -801,12 +801,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>344680</t>
+          <t>344473</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>412268</t>
+          <t>412634</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -816,12 +816,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>25,78%</t>
+          <t>25,77%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>30,84%</t>
+          <t>30,87%</t>
         </is>
       </c>
     </row>
@@ -844,12 +844,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>443432</t>
+          <t>443920</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>491248</t>
+          <t>494001</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -859,12 +859,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>66,23%</t>
+          <t>66,31%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>73,38%</t>
+          <t>73,79%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -879,12 +879,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>468392</t>
+          <t>469157</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>512033</t>
+          <t>513959</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -894,12 +894,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>70,18%</t>
+          <t>70,3%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>76,72%</t>
+          <t>77,01%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -914,12 +914,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>924619</t>
+          <t>924253</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>992207</t>
+          <t>992414</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -929,12 +929,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>69,16%</t>
+          <t>69,13%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>74,22%</t>
+          <t>74,23%</t>
         </is>
       </c>
     </row>
@@ -1074,12 +1074,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>271139</t>
+          <t>269513</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>332905</t>
+          <t>329785</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1089,12 +1089,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>26,55%</t>
+          <t>26,39%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>32,6%</t>
+          <t>32,29%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>244648</t>
+          <t>247357</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>305485</t>
+          <t>303919</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1124,12 +1124,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>23,48%</t>
+          <t>23,74%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>29,32%</t>
+          <t>29,17%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1144,12 +1144,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>532097</t>
+          <t>532666</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>616288</t>
+          <t>616922</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>25,79%</t>
+          <t>25,82%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>29,87%</t>
+          <t>29,9%</t>
         </is>
       </c>
     </row>
@@ -1187,12 +1187,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>688424</t>
+          <t>691544</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>750190</t>
+          <t>751816</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1202,12 +1202,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>67,4%</t>
+          <t>67,71%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>73,45%</t>
+          <t>73,61%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1222,12 +1222,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>736451</t>
+          <t>738017</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>797288</t>
+          <t>794579</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1237,12 +1237,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>70,68%</t>
+          <t>70,83%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>76,52%</t>
+          <t>76,26%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1257,12 +1257,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1446977</t>
+          <t>1446343</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1531168</t>
+          <t>1530599</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1272,12 +1272,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>70,13%</t>
+          <t>70,1%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>74,21%</t>
+          <t>74,18%</t>
         </is>
       </c>
     </row>
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>203617</t>
+          <t>200429</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>253376</t>
+          <t>251231</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1432,12 +1432,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>26,92%</t>
+          <t>26,5%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>33,5%</t>
+          <t>33,21%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1452,12 +1452,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>175356</t>
+          <t>173945</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>222401</t>
+          <t>222268</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1467,12 +1467,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>22,5%</t>
+          <t>22,32%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>28,54%</t>
+          <t>28,52%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1487,12 +1487,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>391016</t>
+          <t>391908</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>462673</t>
+          <t>464774</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1502,12 +1502,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>25,46%</t>
+          <t>25,52%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>30,13%</t>
+          <t>30,26%</t>
         </is>
       </c>
     </row>
@@ -1530,12 +1530,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>503063</t>
+          <t>505208</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>552822</t>
+          <t>556010</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1545,12 +1545,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>66,5%</t>
+          <t>66,79%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>73,08%</t>
+          <t>73,5%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1565,12 +1565,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>556904</t>
+          <t>557037</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>603949</t>
+          <t>605360</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1580,12 +1580,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>71,46%</t>
+          <t>71,48%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>77,5%</t>
+          <t>77,68%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1600,12 +1600,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1073071</t>
+          <t>1070970</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1144728</t>
+          <t>1143836</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1615,12 +1615,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>69,87%</t>
+          <t>69,74%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>74,54%</t>
+          <t>74,48%</t>
         </is>
       </c>
     </row>
@@ -1760,12 +1760,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>271200</t>
+          <t>271184</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>323922</t>
+          <t>328746</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1780,7 +1780,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>34,7%</t>
+          <t>35,22%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1795,12 +1795,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>249316</t>
+          <t>249257</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>309195</t>
+          <t>307235</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1815,7 +1815,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>29,75%</t>
+          <t>29,56%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1830,12 +1830,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>535938</t>
+          <t>535969</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>620546</t>
+          <t>617569</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1845,12 +1845,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>27,16%</t>
+          <t>27,17%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>31,45%</t>
+          <t>31,3%</t>
         </is>
       </c>
     </row>
@@ -1873,12 +1873,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>609551</t>
+          <t>604727</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>662273</t>
+          <t>662289</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1888,7 +1888,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>65,3%</t>
+          <t>64,78%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1908,12 +1908,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>730272</t>
+          <t>732232</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>790151</t>
+          <t>790210</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1923,7 +1923,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>70,25%</t>
+          <t>70,44%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -1943,12 +1943,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1352394</t>
+          <t>1355371</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1437002</t>
+          <t>1436971</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1958,12 +1958,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>68,55%</t>
+          <t>68,7%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>72,84%</t>
+          <t>72,83%</t>
         </is>
       </c>
     </row>
@@ -2103,12 +2103,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>977737</t>
+          <t>974570</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>1087075</t>
+          <t>1080195</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2118,12 +2118,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>28,92%</t>
+          <t>28,83%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>32,15%</t>
+          <t>31,95%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2138,12 +2138,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>877838</t>
+          <t>877364</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>976656</t>
+          <t>988351</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2153,12 +2153,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>24,88%</t>
+          <t>24,87%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>27,68%</t>
+          <t>28,01%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2173,12 +2173,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1880581</t>
+          <t>1881644</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>2033723</t>
+          <t>2035801</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2188,12 +2188,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>27,22%</t>
+          <t>27,24%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>29,44%</t>
+          <t>29,47%</t>
         </is>
       </c>
     </row>
@@ -2216,12 +2216,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2293658</t>
+          <t>2300538</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2402996</t>
+          <t>2406163</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2231,12 +2231,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>67,85%</t>
+          <t>68,05%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>71,08%</t>
+          <t>71,17%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2251,12 +2251,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2551448</t>
+          <t>2539753</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>2650266</t>
+          <t>2650740</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2266,12 +2266,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>72,32%</t>
+          <t>71,99%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>75,12%</t>
+          <t>75,13%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2286,12 +2286,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>4875114</t>
+          <t>4873036</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>5028256</t>
+          <t>5027193</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2301,12 +2301,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>70,56%</t>
+          <t>70,53%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>72,78%</t>
+          <t>72,76%</t>
         </is>
       </c>
     </row>
@@ -2673,32 +2673,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>266842</t>
+          <t>287114</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>239648</t>
+          <t>258387</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>295651</t>
+          <t>314410</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>42,45%</t>
+          <t>42,02%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>38,12%</t>
+          <t>37,81%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>47,03%</t>
+          <t>46,01%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2708,32 +2708,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>270726</t>
+          <t>290667</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>249991</t>
+          <t>268860</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>290294</t>
+          <t>313305</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>40,39%</t>
+          <t>39,99%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>37,3%</t>
+          <t>36,99%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>43,31%</t>
+          <t>43,1%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2743,32 +2743,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>537568</t>
+          <t>577781</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>505380</t>
+          <t>541756</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>572669</t>
+          <t>614627</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>41,39%</t>
+          <t>40,97%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>38,91%</t>
+          <t>38,42%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>44,09%</t>
+          <t>43,59%</t>
         </is>
       </c>
     </row>
@@ -2786,32 +2786,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>361777</t>
+          <t>396203</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>332968</t>
+          <t>368907</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>388971</t>
+          <t>424930</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>57,55%</t>
+          <t>57,98%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>52,97%</t>
+          <t>53,99%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>61,88%</t>
+          <t>62,19%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2821,32 +2821,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>399510</t>
+          <t>436176</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>379942</t>
+          <t>413538</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>420245</t>
+          <t>457983</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>59,61%</t>
+          <t>60,01%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>56,69%</t>
+          <t>56,9%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>62,7%</t>
+          <t>63,01%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2856,32 +2856,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>761287</t>
+          <t>832378</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>726186</t>
+          <t>795532</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>793475</t>
+          <t>868403</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>58,61%</t>
+          <t>59,03%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>55,91%</t>
+          <t>56,41%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>61,09%</t>
+          <t>61,58%</t>
         </is>
       </c>
     </row>
@@ -2899,17 +2899,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>628619</t>
+          <t>683317</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>628619</t>
+          <t>683317</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>628619</t>
+          <t>683317</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2934,17 +2934,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>670236</t>
+          <t>726843</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>670236</t>
+          <t>726843</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>670236</t>
+          <t>726843</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -2969,17 +2969,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>1298855</t>
+          <t>1410159</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1298855</t>
+          <t>1410159</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>1298855</t>
+          <t>1410159</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -3016,32 +3016,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>713006</t>
+          <t>513180</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>576343</t>
+          <t>476007</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>947872</t>
+          <t>549159</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>59,84%</t>
+          <t>48,99%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>48,37%</t>
+          <t>45,44%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>79,55%</t>
+          <t>52,43%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3051,32 +3051,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>402187</t>
+          <t>442968</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>373498</t>
+          <t>412937</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>428954</t>
+          <t>472696</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>42,35%</t>
+          <t>41,67%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>39,33%</t>
+          <t>38,84%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>45,16%</t>
+          <t>44,47%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3086,32 +3086,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>1115192</t>
+          <t>956149</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>968336</t>
+          <t>906166</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1497473</t>
+          <t>998375</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>52,08%</t>
+          <t>45,3%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>45,22%</t>
+          <t>42,94%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>69,93%</t>
+          <t>47,31%</t>
         </is>
       </c>
     </row>
@@ -3129,32 +3129,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>478509</t>
+          <t>534257</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>243643</t>
+          <t>498278</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>615172</t>
+          <t>571430</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>40,16%</t>
+          <t>51,01%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>20,45%</t>
+          <t>47,57%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>51,63%</t>
+          <t>54,56%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3164,32 +3164,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>547568</t>
+          <t>620080</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>520801</t>
+          <t>590352</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>576257</t>
+          <t>650111</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>57,65%</t>
+          <t>58,33%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>54,84%</t>
+          <t>55,53%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>60,67%</t>
+          <t>61,16%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3199,32 +3199,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>1026078</t>
+          <t>1154337</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>643797</t>
+          <t>1112111</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1172934</t>
+          <t>1204320</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>47,92%</t>
+          <t>54,7%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>30,07%</t>
+          <t>52,69%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>54,78%</t>
+          <t>57,06%</t>
         </is>
       </c>
     </row>
@@ -3242,17 +3242,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1191515</t>
+          <t>1047437</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1191515</t>
+          <t>1047437</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1191515</t>
+          <t>1047437</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -3277,17 +3277,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>949755</t>
+          <t>1063048</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>949755</t>
+          <t>1063048</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>949755</t>
+          <t>1063048</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3312,17 +3312,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>2141270</t>
+          <t>2110486</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>2141270</t>
+          <t>2110486</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>2141270</t>
+          <t>2110486</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -3359,32 +3359,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>384706</t>
+          <t>429625</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>356589</t>
+          <t>398099</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>414028</t>
+          <t>466853</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>54,59%</t>
+          <t>53,5%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>50,6%</t>
+          <t>49,57%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>58,75%</t>
+          <t>58,13%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3394,32 +3394,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>337565</t>
+          <t>395424</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>178497</t>
+          <t>368540</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>449726</t>
+          <t>421950</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>36,32%</t>
+          <t>48,93%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>19,2%</t>
+          <t>45,61%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>48,38%</t>
+          <t>52,22%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3429,32 +3429,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>722272</t>
+          <t>825048</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>453826</t>
+          <t>783306</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>844556</t>
+          <t>868955</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>44,2%</t>
+          <t>51,21%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>27,77%</t>
+          <t>48,62%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>51,68%</t>
+          <t>53,93%</t>
         </is>
       </c>
     </row>
@@ -3472,32 +3472,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>319974</t>
+          <t>373448</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>290652</t>
+          <t>336220</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>348091</t>
+          <t>404974</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>45,41%</t>
+          <t>46,5%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>41,25%</t>
+          <t>41,87%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>49,4%</t>
+          <t>50,43%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3507,32 +3507,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>591930</t>
+          <t>412641</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>479769</t>
+          <t>386115</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>750998</t>
+          <t>439525</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>63,68%</t>
+          <t>51,07%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>51,62%</t>
+          <t>47,78%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>80,8%</t>
+          <t>54,39%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3542,32 +3542,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>911904</t>
+          <t>786090</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>789620</t>
+          <t>742183</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1180350</t>
+          <t>827832</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>55,8%</t>
+          <t>48,79%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>48,32%</t>
+          <t>46,07%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>72,23%</t>
+          <t>51,38%</t>
         </is>
       </c>
     </row>
@@ -3585,17 +3585,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>704680</t>
+          <t>803073</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>704680</t>
+          <t>803073</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>704680</t>
+          <t>803073</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -3620,17 +3620,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>929495</t>
+          <t>808065</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>929495</t>
+          <t>808065</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>929495</t>
+          <t>808065</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3655,17 +3655,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1634176</t>
+          <t>1611138</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1634176</t>
+          <t>1611138</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1634176</t>
+          <t>1611138</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -3702,32 +3702,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>382590</t>
+          <t>404465</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>349174</t>
+          <t>371138</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>413701</t>
+          <t>439865</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>41,37%</t>
+          <t>40,94%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>37,76%</t>
+          <t>37,57%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>44,73%</t>
+          <t>44,52%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3737,32 +3737,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>370905</t>
+          <t>402018</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>297458</t>
+          <t>374621</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>408269</t>
+          <t>432627</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>34,0%</t>
+          <t>36,06%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>27,27%</t>
+          <t>33,61%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>37,43%</t>
+          <t>38,81%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3772,32 +3772,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>753495</t>
+          <t>806483</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>672675</t>
+          <t>764666</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>808724</t>
+          <t>854510</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>37,38%</t>
+          <t>38,35%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>33,37%</t>
+          <t>36,37%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>40,12%</t>
+          <t>40,64%</t>
         </is>
       </c>
     </row>
@@ -3815,32 +3815,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>542229</t>
+          <t>583501</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>511118</t>
+          <t>548101</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>575645</t>
+          <t>616828</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>58,63%</t>
+          <t>59,06%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>55,27%</t>
+          <t>55,48%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>62,24%</t>
+          <t>62,43%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3850,32 +3850,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>719925</t>
+          <t>712744</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>682561</t>
+          <t>682135</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>793372</t>
+          <t>740141</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>66,0%</t>
+          <t>63,94%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>62,57%</t>
+          <t>61,19%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>72,73%</t>
+          <t>66,39%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3885,32 +3885,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1262154</t>
+          <t>1296245</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1206925</t>
+          <t>1248218</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1342974</t>
+          <t>1338062</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>62,62%</t>
+          <t>61,65%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>59,88%</t>
+          <t>59,36%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>66,63%</t>
+          <t>63,63%</t>
         </is>
       </c>
     </row>
@@ -3928,17 +3928,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>924819</t>
+          <t>987966</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>924819</t>
+          <t>987966</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>924819</t>
+          <t>987966</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -3963,17 +3963,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1090830</t>
+          <t>1114762</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1090830</t>
+          <t>1114762</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1090830</t>
+          <t>1114762</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -3998,17 +3998,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>2015649</t>
+          <t>2102728</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>2015649</t>
+          <t>2102728</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>2015649</t>
+          <t>2102728</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -4045,32 +4045,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>1747144</t>
+          <t>1634384</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1598032</t>
+          <t>1564810</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>2134364</t>
+          <t>1698228</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>50,65%</t>
+          <t>46,41%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>46,32%</t>
+          <t>44,43%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>61,87%</t>
+          <t>48,22%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4080,32 +4080,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>1381383</t>
+          <t>1531076</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1098223</t>
+          <t>1472474</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>1489538</t>
+          <t>1587964</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>37,95%</t>
+          <t>41,24%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>30,17%</t>
+          <t>39,66%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>40,92%</t>
+          <t>42,77%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4115,32 +4115,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>3128528</t>
+          <t>3165460</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>2875021</t>
+          <t>3077618</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>3560702</t>
+          <t>3250344</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>44,13%</t>
+          <t>43,75%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>40,55%</t>
+          <t>42,54%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>50,22%</t>
+          <t>44,93%</t>
         </is>
       </c>
     </row>
@@ -4158,32 +4158,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1702489</t>
+          <t>1887409</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1315269</t>
+          <t>1823565</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1851601</t>
+          <t>1956983</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>49,35%</t>
+          <t>53,59%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>38,13%</t>
+          <t>51,78%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>53,68%</t>
+          <t>55,57%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4193,32 +4193,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>2258933</t>
+          <t>2181642</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2150778</t>
+          <t>2124754</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>2542093</t>
+          <t>2240244</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>62,05%</t>
+          <t>58,76%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>59,08%</t>
+          <t>57,23%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>69,83%</t>
+          <t>60,34%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4228,32 +4228,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>3961421</t>
+          <t>4069051</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>3529247</t>
+          <t>3984167</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>4214928</t>
+          <t>4156893</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>55,87%</t>
+          <t>56,25%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>49,78%</t>
+          <t>55,07%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>59,45%</t>
+          <t>57,46%</t>
         </is>
       </c>
     </row>
@@ -4271,17 +4271,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>3449633</t>
+          <t>3521793</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>3449633</t>
+          <t>3521793</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>3449633</t>
+          <t>3521793</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -4306,17 +4306,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>3640316</t>
+          <t>3712718</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>3640316</t>
+          <t>3712718</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>3640316</t>
+          <t>3712718</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4341,17 +4341,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>7089949</t>
+          <t>7234511</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>7089949</t>
+          <t>7234511</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>7089949</t>
+          <t>7234511</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
